--- a/Resources/import_template.xlsx
+++ b/Resources/import_template.xlsx
@@ -8,10 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="配件导入" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="填写教程" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'配件导入'!$1:$1</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,7 +34,24 @@
     </font>
     <font>
       <name val="微软雅黑"/>
-      <color rgb="00808080"/>
+      <color rgb="00333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="004472C4"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00666666"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -79,13 +95,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -452,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -519,64 +540,311 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>放图片</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>放图片</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>放图片</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>iPhone 15手机壳</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>手机配件</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>透明防摔保护套</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>放图片</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>放图片</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>放图片</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E3:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="价格错误" error="请输入有效价格" promptTitle="商品价格" prompt="请输入商品价格（整数）" type="whole" operator="greaterThanOrEqual">
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="价格错误" error="请输入有效价格（整数）" type="whole" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>缩略图1</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>缩略图2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>缩略图3</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>商品价格</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>商品分类</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>商品详情</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>详情图1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>详情图2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>详情图3</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>填写说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="80" customHeight="1">
+      <c r="A2" s="3" t="n"/>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>iPhone 15手机壳</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>手机配件</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>透明防摔保护套，TPU材质</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>缩略图1-3</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>直接在单元格中插入商品图片</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="80" customHeight="1">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>AirPods Pro保护套</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>耳机配件</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>硅胶材质，多色可选</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>必填，配件的名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="80" customHeight="1">
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>USB-C快充线</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>充电配件</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>1.5米编织线，支持快充</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>商品价格</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>必填，整数金额，如29表示29元</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>商品分类</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>选填，已有分类会自动匹配，新分类会自动创建</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>商品详情</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>选填，配件的文字描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>详情图1-3</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>选填，商品详情页的图片</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="L8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>注意事项</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>在【配件导入】表中填写，不要修改表头</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>缩略图和详情图可以直接粘贴到单元格中</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>图片列没有图片可以留空</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>商品名称和价格为必填项</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>分类名会自动匹配已有分类，不存在则新建</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Resources/import_template.xlsx
+++ b/Resources/import_template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,7 +41,7 @@
       <name val="微软雅黑"/>
       <b val="1"/>
       <color rgb="004472C4"/>
-      <sz val="11"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="微软雅黑"/>
@@ -54,8 +54,19 @@
       <color rgb="00666666"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00CC0000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +77,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,18 +118,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -473,22 +509,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>缩略图1</t>
@@ -506,22 +544,22 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>商品名称</t>
+          <t>商品名称（必填）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>商品价格</t>
+          <t>商品价格（必填）</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>商品分类</t>
+          <t>商品分类（必填）</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>商品详情</t>
+          <t>商品详情（必填）</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -537,6 +575,16 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>详情图3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>详情图4</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>详情图5</t>
         </is>
       </c>
     </row>
@@ -556,24 +604,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>缩略图1</t>
@@ -591,22 +641,22 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>商品名称</t>
+          <t>商品名称（必填）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>商品价格</t>
+          <t>商品价格（必填）</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>商品分类</t>
+          <t>商品分类（必填）</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>商品详情</t>
+          <t>商品详情（必填）</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -624,7 +674,17 @@
           <t>详情图3</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>详情图4</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>详情图5</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>填写说明</t>
         </is>
@@ -655,14 +715,16 @@
       <c r="H2" s="3" t="n"/>
       <c r="I2" s="3" t="n"/>
       <c r="J2" s="3" t="n"/>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>缩略图1-3</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>直接在单元格中插入商品图片</t>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>直接在单元格中插入商品图片，没有可留空</t>
         </is>
       </c>
     </row>
@@ -691,12 +753,14 @@
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>商品名称</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>必填，配件的名称</t>
         </is>
@@ -727,120 +791,131 @@
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>商品价格</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>必填，整数金额，如29表示29元</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="L5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>商品分类</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>选填，已有分类会自动匹配，新分类会自动创建</t>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>已有分类会自动匹配，新分类会自动创建</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="L6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>商品详情</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>选填，配件的文字描述</t>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>配件的文字描述</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>详情图1-3</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>选填，商品详情页的图片</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="L8" s="4" t="inlineStr"/>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>详情图1-5</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>商品详情页的图片，截图后粘贴到单元格，没有可留空</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="L9" s="2" t="inlineStr">
+      <c r="N9" s="6" t="inlineStr">
         <is>
           <t>注意事项</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="L10" s="4" t="inlineStr">
+      <c r="N10" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="O10" s="8" t="inlineStr">
         <is>
           <t>在【配件导入】表中填写，不要修改表头</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="L11" s="4" t="inlineStr">
+      <c r="N11" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="O11" s="8" t="inlineStr">
         <is>
           <t>缩略图和详情图可以直接粘贴到单元格中</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="L12" s="4" t="inlineStr">
+      <c r="N12" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="O12" s="8" t="inlineStr">
         <is>
           <t>图片列没有图片可以留空</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="L13" s="4" t="inlineStr">
+      <c r="N13" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="O13" s="8" t="inlineStr">
         <is>
           <t>商品名称和价格为必填项</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="L14" s="4" t="inlineStr">
+      <c r="N14" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
         <is>
           <t>分类名会自动匹配已有分类，不存在则新建</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>填写完成后保存，在App中选择文件导入即可</t>
         </is>
       </c>
     </row>

--- a/Resources/import_template.xlsx
+++ b/Resources/import_template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,6 +31,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00999999"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="微软雅黑"/>
@@ -66,7 +71,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -77,6 +82,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -118,30 +129,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -509,88 +523,100 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>缩略图1</t>
+          <t>缩略图1(选填)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>缩略图2</t>
+          <t>缩略图2(选填)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>缩略图3</t>
+          <t>缩略图3(选填)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>缩略图4(选填)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>缩略图5(选填)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>商品名称（必填）</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>商品价格（必填）</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>商品分类（必填）</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>商品详情（必填）</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>详情图1</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>详情图2</t>
+          <t>商品详情(选填)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>详情图3</t>
+          <t>详情图1(选填)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>详情图4</t>
+          <t>详情图2(选填)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>详情图5</t>
+          <t>详情图3(选填)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>详情图4(选填)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>详情图5(选填)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="价格错误" error="请输入有效价格（整数）" type="whole" operator="greaterThanOrEqual">
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="请输入有效价格（整数）" type="whole" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -604,316 +630,454 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="55" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>缩略图1</t>
+          <t>缩略图1(选填)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>缩略图2</t>
+          <t>缩略图2(选填)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>缩略图3</t>
+          <t>缩略图3(选填)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>缩略图4(选填)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>缩略图5(选填)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>商品名称（必填）</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>商品价格（必填）</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>商品分类（必填）</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>商品详情（必填）</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>详情图1</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>详情图2</t>
+          <t>商品详情(选填)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>详情图3</t>
+          <t>详情图1(选填)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>详情图4</t>
+          <t>详情图2(选填)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>详情图5</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
+          <t>详情图3(选填)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>详情图4(选填)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>详情图5(选填)</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>填写说明</t>
         </is>
       </c>
     </row>
     <row r="2" ht="80" customHeight="1">
-      <c r="A2" s="3" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>iPhone 15手机壳</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>手机配件</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>透明防摔保护套，TPU材质</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>缩略图1-3</t>
-        </is>
-      </c>
-      <c r="O2" s="5" t="inlineStr">
-        <is>
-          <t>直接在单元格中插入商品图片，没有可留空</t>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>iPhone 15 液态硅胶磁吸保护壳</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>手机壳</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>防摔保护套，液态硅胶材质</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>缩略图1-5</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>直接在单元格中插入商品图片，如不需要展示可以不填</t>
         </is>
       </c>
     </row>
     <row r="3" ht="80" customHeight="1">
-      <c r="A3" s="3" t="n"/>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
           <t>AirPods Pro保护套</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>耳机配件</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>硅胶材质，多色可选</t>
         </is>
       </c>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>商品名称</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="Q3" s="6" t="inlineStr">
         <is>
           <t>必填，配件的名称</t>
         </is>
       </c>
     </row>
     <row r="4" ht="80" customHeight="1">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
           <t>USB-C快充线</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>充电配件</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>充电线</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>1.5米编织线，支持快充</t>
         </is>
       </c>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>嵌入图片到单元格</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>商品价格</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>必填，整数金额，如29表示29元</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="N5" s="4" t="inlineStr">
+      <c r="P5" s="5" t="inlineStr">
         <is>
           <t>商品分类</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>已有分类会自动匹配，新分类会自动创建</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="N6" s="4" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
         <is>
           <t>商品详情</t>
         </is>
       </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>配件的文字描述</t>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>选填，配件的文字描述（如详情页有图片文字介绍，可以不填）</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="N7" s="4" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>详情图1-5</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>商品详情页的图片，截图后粘贴到单元格，没有可留空</t>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>选填，有几张可以填几张，商品详情页的图片，跟网店的长图一样（不需要详细可不填）</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="N9" s="6" t="inlineStr">
+      <c r="P9" s="7" t="inlineStr">
         <is>
           <t>注意事项</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="N10" s="7" t="inlineStr">
+      <c r="P10" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O10" s="8" t="inlineStr">
+      <c r="Q10" s="9" t="inlineStr">
         <is>
           <t>在【配件导入】表中填写，不要修改表头</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="N11" s="7" t="inlineStr">
+      <c r="P11" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O11" s="8" t="inlineStr">
-        <is>
-          <t>缩略图和详情图可以直接粘贴到单元格中</t>
+      <c r="Q11" s="9" t="inlineStr">
+        <is>
+          <t>缩略图和详情图可以嵌入图片到单元格</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="N12" s="7" t="inlineStr">
+      <c r="P12" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="Q12" s="9" t="inlineStr">
         <is>
           <t>图片列没有图片可以留空</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="N13" s="7" t="inlineStr">
+      <c r="P13" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
+      <c r="Q13" s="9" t="inlineStr">
         <is>
           <t>商品名称和价格为必填项</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="N14" s="7" t="inlineStr">
+      <c r="P14" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
-        <is>
-          <t>分类名会自动匹配已有分类，不存在则新建</t>
+      <c r="Q14" s="9" t="inlineStr">
+        <is>
+          <t>分类名会自动匹配已有分类，不存在则自动新建</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="N15" s="7" t="inlineStr">
+      <c r="P15" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="Q15" s="9" t="inlineStr">
         <is>
           <t>填写完成后保存，在App中选择文件导入即可</t>
         </is>
